--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260623.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260623.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>134,413,000</t>
+          <t>133,741,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.62%</t>
+          <t>15.75%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3,218,000</t>
+          <t>3,194,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>10.03%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.18%</t>
+          <t>6.07%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5.93%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.44%</t>
+          <t>5.21%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.52%</t>
+          <t>4.17%</t>
         </is>
       </c>
     </row>
@@ -748,95 +748,95 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.16%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>7,952,000</t>
+          <t>7,813,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7,813,000</t>
+          <t>7,952,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>8,655,000</t>
+          <t>19,329,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>19,329,000</t>
+          <t>8,655,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>14,170,000</t>
+          <t>15,094,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>15,094,000</t>
+          <t>14,170,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1056,51 +1056,51 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,180,703,214</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>2,027,877,264</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1166,95 +1166,95 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,083,000</t>
+          <t>7,540,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>7,540,000</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>202607WTX</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>115/07台股期貨</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>2,664,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,664,000</t>
+          <t>14,421,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1276,51 +1276,51 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,930,000</t>
+          <t>14,278,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,278,000</t>
+          <t>1,930,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,024,230,378</t>
+          <t>992,518,378</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1364,46 +1364,46 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>群光電子</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>6,681,000</t>
+          <t>1,755,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>群光電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,755,000</t>
+          <t>6,681,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,44 +1415,44 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,075,000</t>
+          <t>3,412,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>4,075,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1635,66 +1635,66 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富邦媒體</t>
+          <t>美律實業</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>770,000</t>
+          <t>2,440,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>美律實業</t>
+          <t>中磊電子</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,440,000</t>
+          <t>2,315,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>中磊電子</t>
+          <t>富邦媒體</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,365,000</t>
+          <t>295,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>197,000</t>
+          <t>159,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>223,000</t>
+          <t>172,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-372,044,019</t>
+          <t>-629,631,891</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.44%</t>
         </is>
       </c>
     </row>
